--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1228 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +923,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1092,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1133,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2610,22 +2642,22 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2658,12 +2690,12 @@
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2745,1232 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -780,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -872,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -899,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1097,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1125,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1807,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1846,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1885,12 +1925,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1926,10 +1966,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2029,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2636,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2747,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2858,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2969,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,7 +3080,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3139,7 +3191,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3250,7 +3302,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3361,7 +3413,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3472,7 +3524,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3583,7 +3635,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3651,7 +3703,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3694,7 +3746,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3708,7 +3760,7 @@
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3738,13 +3790,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3861,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3877,7 +3933,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3920,7 +3976,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3934,7 +3990,7 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3969,6 +4025,803 @@
       </c>
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
         </is>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1703,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1847,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,17 +1883,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1891,13 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1946,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq61，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1958,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2048,32 +2064,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2081,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2105,33 +2125,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -2159,32 +2183,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2192,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2216,33 +2244,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2414,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2453,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2525,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2636,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2747,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3223,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,7 +3334,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3445,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3524,7 +3556,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3746,7 +3778,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3800,7 +3832,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3893,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3976,7 +4008,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4087,7 +4119,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4141,7 +4173,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4234,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4313,7 +4345,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4367,7 +4399,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4460,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4482,7 +4514,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4575,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4597,7 +4629,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4690,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4712,7 +4744,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4720,22 +4752,22 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4773,7 +4805,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4817,11 +4849,582 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr"/>
-      <c r="AC38" s="2" t="inlineStr">
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
         </is>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2413,32 +2413,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2446,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2470,17 +2474,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2490,13 +2494,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -2524,32 +2532,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2557,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,33 +2593,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -2635,32 +2651,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2668,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,33 +2712,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -2746,32 +2770,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2779,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,33 +2831,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2889,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2890,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2914,33 +2950,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3112,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3262,7 +3302,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3334,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3832,7 +3872,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4008,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,7 +4159,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4173,7 +4213,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4274,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4385,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4399,7 +4439,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4500,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4514,7 +4554,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4615,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4629,7 +4669,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4730,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4744,7 +4784,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4845,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4859,7 +4899,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4960,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4974,7 +5014,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5075,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5089,7 +5129,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5190,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5204,7 +5244,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5305,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5309,13 +5349,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5420,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5430,6 +5474,577 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,18 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1664,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2742,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -3119,32 +3123,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,33 +3184,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3230,32 +3242,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3263,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3287,17 +3303,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3307,13 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3341,32 +3361,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3374,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,17 +3422,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3418,13 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3452,32 +3480,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3485,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3509,17 +3541,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3529,13 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3674,32 +3710,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3707,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3731,33 +3771,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3785,32 +3829,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3818,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3842,17 +3890,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3862,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3987,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4015,32 +4063,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4048,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4072,33 +4124,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4126,32 +4182,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4159,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4183,37 +4243,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4301,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4274,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4282,10 +4342,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4385,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4439,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4554,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4669,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4769,7 +4845,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4784,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4899,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5014,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5129,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5244,7 +5320,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5359,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5496,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5531,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5585,7 +5661,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5700,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5815,7 +5891,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5930,7 +6006,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -5938,22 +6014,22 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -5986,12 +6062,12 @@
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6005,43 +6081,733 @@
       <c r="T48" s="2" t="inlineStr"/>
       <c r="U48" s="2" t="inlineStr">
         <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
           <t>11:20</t>
         </is>
       </c>
-      <c r="V48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr">
+      <c r="W49" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X48" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y48" s="2" t="inlineStr">
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="Z49" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr"/>
-      <c r="AC48" s="2" t="inlineStr">
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2383,13 +2383,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2502,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2616,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2627,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3099,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3333,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,7 +3686,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3801,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4154,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4310,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4334,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4404,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4428,32 +4432,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4461,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4485,17 +4493,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4505,17 +4513,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4551,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4576,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4600,17 +4612,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4620,17 +4632,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4745,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4773,32 +4785,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4806,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4846,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4850,17 +4866,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5003,32 +5019,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5036,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,17 +5080,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5080,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5118,32 +5138,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5151,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,17 +5199,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5195,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5233,32 +5257,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5266,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5290,37 +5318,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5348,32 +5376,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5381,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5405,17 +5437,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5425,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5463,32 +5495,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5496,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5520,17 +5556,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5540,13 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5661,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5801,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5776,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5891,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6006,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6121,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6236,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6347,7 +6387,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6462,7 +6502,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6577,7 +6617,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6678,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6692,7 +6732,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6793,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6797,17 +6837,695 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>11/27</t>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>144.5</t>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,17 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,22 +2973,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,22 +3203,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,14 +3441,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,18 +3675,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3924,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4876,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5348,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,14 +5456,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>144.5</t>
@@ -5467,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5647,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5729,32 +5733,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5762,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5786,17 +5794,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5806,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5844,32 +5852,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -5877,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5901,17 +5913,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5921,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5959,32 +5971,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5992,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,37 +6032,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6074,32 +6090,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6107,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,37 +6151,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6189,32 +6209,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6222,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6246,17 +6270,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6266,17 +6290,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6304,32 +6328,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6337,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6361,33 +6389,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6563,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6617,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6732,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6847,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6962,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7299,7 +7331,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7515,17 +7547,592 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>142.0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>11/29</t>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>153.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,14 +1426,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,18 +2029,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2631,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2988,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3456,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3690,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3803,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,14 +3917,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>153.0</t>
@@ -3928,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,17 +4151,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,12 +4275,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4473,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,14 +4516,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -4527,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5352,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5824,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6062,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6181,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6419,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6447,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6480,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6504,17 +6512,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6524,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6562,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6595,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6619,32 +6631,32 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6677,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6710,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,17 +6750,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6754,12 +6770,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6792,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6825,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,37 +6869,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6907,32 +6927,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6940,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,17 +6988,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6984,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7022,12 +7046,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq37推进至seq49，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7055,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7063,10 +7087,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
       <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7133,32 +7165,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7166,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7190,33 +7226,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7331,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7503,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7557,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7672,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7787,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7902,7 +7942,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7963,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8017,7 +8057,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8132,7 +8172,582 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
           <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,14 +2267,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,14 +5222,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6818,24 +6818,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6949,12 +6949,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq37推进至seq49，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq37推进至seq57，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7175,24 +7175,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7284,32 +7284,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7317,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7345,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7361,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7399,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7432,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7456,17 +7464,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7476,13 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7510,32 +7522,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7543,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,17 +7583,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7587,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7625,32 +7641,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7658,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,17 +7702,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7702,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7827,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7942,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8057,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8172,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8402,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8512,12 +8532,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8632,7 +8652,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8742,12 +8762,575 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>142.3</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,14 +1902,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,14 +4270,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>142.3</t>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,14 +6289,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,14 +6765,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>142.3</t>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7760,32 +7760,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7793,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,17 +7821,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7837,17 +7841,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7875,32 +7879,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7908,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,17 +7940,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7952,12 +7960,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7990,32 +7998,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8023,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8047,17 +8059,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8067,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8105,32 +8117,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8138,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,17 +8178,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8182,17 +8198,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8307,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8483,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8537,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8652,7 +8668,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8828,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8939,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9054,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9112,22 +9128,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9160,12 +9176,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9204,22 +9220,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9243,7 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -9237,7 +9253,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -9275,12 +9291,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9294,43 +9310,1078 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr"/>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,14 +2148,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,22 +4516,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,14 +5813,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,14 +6170,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,14 +7360,14 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,14 +7598,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8127,24 +8127,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8193,22 +8193,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8236,32 +8236,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8269,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8297,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8313,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8423,7 +8427,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8466,32 +8470,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8499,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,17 +8531,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8543,12 +8551,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8581,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8614,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,37 +8650,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8696,32 +8708,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8729,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8753,17 +8769,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8773,12 +8789,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8811,12 +8827,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq43，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8844,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8852,10 +8868,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8922,32 +8954,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -8955,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8979,17 +9015,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -8999,12 +9035,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9070,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9181,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9296,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9350,7 +9386,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9522,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9637,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9752,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9806,7 +9842,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9921,7 +9957,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9982,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10097,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10212,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10327,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10381,7 +10417,927 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
           <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3092,18 +3092,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3287,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3406,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3568,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4231,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4988,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4994,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5464,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5540,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5655,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6726,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6964,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7202,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,7 +7245,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7321,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7440,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7559,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7678,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,7 +7721,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7797,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8154,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8388,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8442,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8745,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8784,7 +8788,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8832,7 +8836,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq43，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8860,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8964,24 +8968,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8991,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9030,7 +9034,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9040,12 +9044,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9073,32 +9077,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9106,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9130,33 +9138,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9184,32 +9196,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9217,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,37 +9257,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9299,32 +9315,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9332,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,17 +9376,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9376,17 +9396,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9673,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9727,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9903,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9942,7 +9962,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10018,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10133,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10187,7 +10207,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10363,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10478,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10593,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10708,7 +10728,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10823,7 +10843,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10938,7 +10958,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11053,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11107,7 +11127,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11188,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11283,7 +11303,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11341,6 +11361,811 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,14 +2267,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3330,22 +3330,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,14 +5226,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6531,22 +6531,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6774,17 +6774,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9391,14 +9391,14 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9545,32 +9545,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9578,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,37 +9606,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9732,7 +9736,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9775,32 +9779,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9808,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,37 +9840,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9890,32 +9898,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9923,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9947,17 +9959,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9967,17 +9979,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10005,32 +10017,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10038,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10062,37 +10078,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10192,7 +10208,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10207,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10235,32 +10251,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10268,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10292,17 +10312,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10312,17 +10332,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10422,7 +10442,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10437,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10552,7 +10572,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10667,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10782,7 +10802,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10897,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11012,7 +11032,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11188,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11242,7 +11262,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11323,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11357,7 +11377,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11533,7 +11553,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11587,7 +11607,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11668,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11763,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11817,7 +11837,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11898,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11932,7 +11952,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11993,7 +12013,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12055,22 +12075,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12103,12 +12123,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12122,47 +12142,852 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W100" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z100" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>7/30</t>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,22 +2858,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,22 +5936,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7369,17 +7369,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10485,32 +10485,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10518,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10542,17 +10546,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10562,17 +10566,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10637,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10687,7 +10691,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10715,32 +10719,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10748,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10772,37 +10780,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10830,32 +10838,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10863,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10887,17 +10899,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10907,17 +10919,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10945,32 +10957,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10978,7 +10994,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11002,17 +11018,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11022,12 +11038,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11060,32 +11076,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11093,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11117,17 +11137,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11137,17 +11157,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11175,32 +11195,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11208,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11232,17 +11256,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11252,12 +11276,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11290,32 +11314,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11323,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11347,17 +11375,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11367,17 +11395,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11520,32 +11548,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -11553,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11577,37 +11609,37 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11783,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11837,7 +11869,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12013,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12067,7 +12099,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12243,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12297,7 +12329,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12390,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12473,7 +12505,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12588,7 +12620,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12642,7 +12674,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12735,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12818,7 +12850,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12872,7 +12904,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -12880,22 +12912,22 @@
       <c r="A106" s="2" t="inlineStr"/>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -12928,12 +12960,12 @@
       <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12947,47 +12979,392 @@
       <c r="T106" s="2" t="inlineStr"/>
       <c r="U106" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W106" s="2" t="inlineStr">
+      <c r="W107" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X106" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y106" s="2" t="inlineStr">
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z106" s="2" t="inlineStr">
+      <c r="Z107" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA106" s="2" t="inlineStr">
+      <c r="AA107" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB106" s="2" t="inlineStr">
+      <c r="AB107" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="AC106" s="2" t="inlineStr">
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
         <is>
           <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>129.7</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3097,17 +3097,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7726,17 +7726,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9979,17 +9979,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11667,32 +11667,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11700,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11724,17 +11728,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11744,17 +11748,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11786,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11815,7 +11823,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11839,17 +11847,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11859,17 +11867,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11897,32 +11905,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11930,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11954,17 +11966,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11974,17 +11986,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12057,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12127,12 +12139,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -12160,7 +12172,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12168,10 +12180,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="2" t="inlineStr"/>
-      <c r="S99" s="2" t="inlineStr"/>
-      <c r="T99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12214,7 +12242,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12242,32 +12270,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12275,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12299,17 +12331,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12319,17 +12351,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12357,32 +12389,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12390,7 +12426,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12414,17 +12450,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12434,17 +12470,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12541,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12559,7 +12595,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12587,12 +12623,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -12620,7 +12656,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12628,10 +12664,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q103" s="2" t="inlineStr"/>
-      <c r="R103" s="2" t="inlineStr"/>
-      <c r="S103" s="2" t="inlineStr"/>
-      <c r="T103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12674,7 +12726,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12787,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12789,7 +12841,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12850,7 +12902,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12965,7 +13017,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13019,7 +13071,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13132,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13134,7 +13186,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13247,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13249,7 +13301,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13362,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">

--- a/data/export/2026-09-29-浦东35路.xlsx
+++ b/data/export/2026-09-29-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2744,17 +2744,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2982,17 +2982,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7964,17 +7964,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9741,17 +9741,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10213,17 +10213,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12754,32 +12754,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12787,7 +12791,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12811,17 +12815,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12831,17 +12835,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12869,32 +12873,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12902,7 +12910,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12926,17 +12934,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12946,17 +12954,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12984,32 +12992,36 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -13017,7 +13029,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13041,17 +13053,17 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
@@ -13061,17 +13073,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13144,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13247,7 +13259,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13362,7 +13374,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
